--- a/artfynd/A 7098-2025 artfynd.xlsx
+++ b/artfynd/A 7098-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>122369561</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7098-2025 artfynd.xlsx
+++ b/artfynd/A 7098-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73282242</v>
+        <v>78279581</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horntjärnsmyren, Vrm</t>
+          <t>Gyltamossarna, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387255.7931244725</v>
+        <v>387231</v>
       </c>
       <c r="R2" t="n">
-        <v>6648508.224340023</v>
+        <v>6648599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2019-06-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,33 +765,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78279581</v>
+        <v>73282242</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,45 +795,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gyltamossarna, Vrm</t>
+          <t>Horntjärnsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387231.4460648706</v>
+        <v>387256</v>
       </c>
       <c r="R3" t="n">
-        <v>6648598.672615796</v>
+        <v>6648508</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,22 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-03</t>
+          <t>2018-09-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-03</t>
+          <t>2018-09-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,19 +873,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -914,12 +894,7 @@
         <v>122369561</v>
       </c>
       <c r="B4" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,6 +998,113 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>73282243</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Horntjärnsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>387268</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6648606</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2018-09-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2018-09-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
